--- a/data/EEZ_074/EEZ_074.xlsx
+++ b/data/EEZ_074/EEZ_074.xlsx
@@ -10,8 +10,12 @@
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Catch" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="SPPR" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="PPR" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="NPP" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="sppr_all" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="sppr_inner" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="sppr_PP" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Recycling" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="PPR" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="NPP" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,13 +40,22 @@
       <b val="1"/>
       <sz val="14"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -57,7 +70,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -68,6 +81,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -434,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -512,235 +532,266 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>catch years</t>
+          <t>model workbooks</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2004-2019</t>
+          <t>none yet</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>taxa in catch</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>15</v>
+          <t>catch years</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2004-2019</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>taxa in catch</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>taxa with a trophic level</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B11" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>model source context</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>No pilot model selected</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>catch_tonnes</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>ppr_tonnes</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>ppr_over_npp_percent</t>
         </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>2004</v>
-      </c>
-      <c r="B13" t="n">
-        <v>2.115</v>
-      </c>
-      <c r="C13" t="n">
-        <v>422.692</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>2005</v>
-      </c>
-      <c r="B14" t="n">
-        <v>17.481</v>
-      </c>
-      <c r="C14" t="n">
-        <v>3753.776</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2006</v>
+        <v>2004</v>
       </c>
       <c r="B15" t="n">
-        <v>55.746</v>
+        <v>2.115</v>
       </c>
       <c r="C15" t="n">
-        <v>11496.627</v>
+        <v>422.692</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="B16" t="n">
-        <v>40.136</v>
+        <v>17.481</v>
       </c>
       <c r="C16" t="n">
-        <v>8628.627</v>
+        <v>3753.776</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="B17" t="n">
-        <v>35.49</v>
+        <v>55.746</v>
       </c>
       <c r="C17" t="n">
-        <v>7000.356</v>
+        <v>11496.627</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="B18" t="n">
-        <v>70.419</v>
+        <v>40.136</v>
       </c>
       <c r="C18" t="n">
-        <v>13680.56</v>
+        <v>8628.627</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="B19" t="n">
-        <v>135.566</v>
+        <v>35.49</v>
       </c>
       <c r="C19" t="n">
-        <v>26613.452</v>
+        <v>7000.356</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="B20" t="n">
-        <v>182.344</v>
+        <v>70.419</v>
       </c>
       <c r="C20" t="n">
-        <v>35477.48</v>
+        <v>13680.56</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="B21" t="n">
-        <v>97.72799999999999</v>
+        <v>135.566</v>
       </c>
       <c r="C21" t="n">
-        <v>19067.109</v>
+        <v>26613.452</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="B22" t="n">
-        <v>104.924</v>
+        <v>182.344</v>
       </c>
       <c r="C22" t="n">
-        <v>21421.483</v>
+        <v>35477.48</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="B23" t="n">
-        <v>42.112</v>
+        <v>97.72799999999999</v>
       </c>
       <c r="C23" t="n">
-        <v>8131.249</v>
+        <v>19067.109</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="B24" t="n">
-        <v>75.461</v>
+        <v>104.924</v>
       </c>
       <c r="C24" t="n">
-        <v>14810.786</v>
+        <v>21421.483</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="B25" t="n">
-        <v>83.932</v>
+        <v>42.112</v>
       </c>
       <c r="C25" t="n">
-        <v>16755.395</v>
+        <v>8131.249</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="B26" t="n">
-        <v>145.083</v>
+        <v>75.461</v>
       </c>
       <c r="C26" t="n">
-        <v>28257.898</v>
+        <v>14810.786</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="B27" t="n">
-        <v>171.287</v>
+        <v>83.932</v>
       </c>
       <c r="C27" t="n">
-        <v>33833.413</v>
+        <v>16755.395</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B28" t="n">
+        <v>145.083</v>
+      </c>
+      <c r="C28" t="n">
+        <v>28257.898</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B29" t="n">
+        <v>171.287</v>
+      </c>
+      <c r="C29" t="n">
+        <v>33833.413</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
         <v>2019</v>
       </c>
-      <c r="B28" t="n">
+      <c r="B30" t="n">
         <v>133.561</v>
       </c>
-      <c r="C28" t="n">
+      <c r="C30" t="n">
         <v>25983.664</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>PPR/NPP converts wet-weight PP to carbon at 9:1; NPP is the fixed 2019 ensemble median.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>PPR/NPP is blank because no NPP estimate exists for this ecosystem.</t>
         </is>
@@ -803,85 +854,53 @@
           <t>commercial_group</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>2004</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>2005</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
-      </c>
-      <c r="K1" s="2" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="M1" s="2" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="N1" s="2" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="O1" s="2" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="P1" s="2" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="Q1" s="2" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="R1" s="2" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="S1" s="2" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="T1" s="2" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="E1" s="2" t="n">
+        <v>2004</v>
+      </c>
+      <c r="F1" s="2" t="n">
+        <v>2005</v>
+      </c>
+      <c r="G1" s="2" t="n">
+        <v>2006</v>
+      </c>
+      <c r="H1" s="2" t="n">
+        <v>2007</v>
+      </c>
+      <c r="I1" s="2" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J1" s="2" t="n">
+        <v>2009</v>
+      </c>
+      <c r="K1" s="2" t="n">
+        <v>2010</v>
+      </c>
+      <c r="L1" s="2" t="n">
+        <v>2011</v>
+      </c>
+      <c r="M1" s="2" t="n">
+        <v>2012</v>
+      </c>
+      <c r="N1" s="2" t="n">
+        <v>2013</v>
+      </c>
+      <c r="O1" s="2" t="n">
+        <v>2014</v>
+      </c>
+      <c r="P1" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="Q1" s="2" t="n">
+        <v>2016</v>
+      </c>
+      <c r="R1" s="2" t="n">
+        <v>2017</v>
+      </c>
+      <c r="S1" s="2" t="n">
+        <v>2018</v>
+      </c>
+      <c r="T1" s="2" t="n">
+        <v>2019</v>
       </c>
     </row>
     <row r="2">
@@ -2136,6 +2155,245 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Group SPPR: all</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>All basal sources, including imports. Models are separate. Blank means unavailable, not zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>group_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>No extracted model is available for this ecosystem.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Group SPPR: inner</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Internal sources: primary producers and detritus; excludes imports. Models are separate. Blank means unavailable, not zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>group_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>No extracted model is available for this ecosystem.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Group SPPR: PP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Primary producers only; excludes detritus and imports. Models are separate. Blank means unavailable, not zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>group_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>No extracted model is available for this ecosystem.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="90" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Recycling diagnostics from diagnose_sppr()</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>b: detrital recycling; rho living: living food-web cycles. Each must be below 1 for convergence; these are necessary, not sufficient checks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>TE_option</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>rho living</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>diagnostic status</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>b converges</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>living converges</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>input balanced</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>configuration</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2206,85 +2464,53 @@
           <t>trophic_level</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>2004</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>2005</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="Q4" s="3" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="R4" s="3" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="C4" s="3" t="n">
+        <v>2004</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>2005</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>2006</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>2007</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>2008</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>2009</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>2011</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>2012</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>2013</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>2014</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>2015</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>2017</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>2018</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>2019</v>
       </c>
     </row>
     <row r="5">
@@ -2872,7 +3098,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/data/EEZ_074/EEZ_074.xlsx
+++ b/data/EEZ_074/EEZ_074.xlsx
@@ -9,15 +9,18 @@
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Catch" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="SPPR" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="sppr_all" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="sppr_inner" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="sppr_PP" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Recycling" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="PPR" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="NPP" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Final mappings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="SPPR" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="sppr_all" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="sppr_inner" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="sppr_PP" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Recycling" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="PPR" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="NPP" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'NPP'!$A$3:$O$25</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -454,13 +457,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -617,6 +620,9 @@
       <c r="C15" t="n">
         <v>422.692</v>
       </c>
+      <c r="D15" t="n">
+        <v>0.0002</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -628,6 +634,9 @@
       <c r="C16" t="n">
         <v>3753.776</v>
       </c>
+      <c r="D16" t="n">
+        <v>0.0015</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -639,6 +648,9 @@
       <c r="C17" t="n">
         <v>11496.627</v>
       </c>
+      <c r="D17" t="n">
+        <v>0.0054</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -650,6 +662,9 @@
       <c r="C18" t="n">
         <v>8628.627</v>
       </c>
+      <c r="D18" t="n">
+        <v>0.0039</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -661,6 +676,9 @@
       <c r="C19" t="n">
         <v>7000.356</v>
       </c>
+      <c r="D19" t="n">
+        <v>0.0035</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -672,6 +690,9 @@
       <c r="C20" t="n">
         <v>13680.56</v>
       </c>
+      <c r="D20" t="n">
+        <v>0.0059</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -683,6 +704,9 @@
       <c r="C21" t="n">
         <v>26613.452</v>
       </c>
+      <c r="D21" t="n">
+        <v>0.0105</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -694,6 +718,9 @@
       <c r="C22" t="n">
         <v>35477.48</v>
       </c>
+      <c r="D22" t="n">
+        <v>0.0153</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -705,6 +732,9 @@
       <c r="C23" t="n">
         <v>19067.109</v>
       </c>
+      <c r="D23" t="n">
+        <v>0.008500000000000001</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -716,6 +746,9 @@
       <c r="C24" t="n">
         <v>21421.483</v>
       </c>
+      <c r="D24" t="n">
+        <v>0.009299999999999999</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -727,6 +760,9 @@
       <c r="C25" t="n">
         <v>8131.249</v>
       </c>
+      <c r="D25" t="n">
+        <v>0.0037</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -738,6 +774,9 @@
       <c r="C26" t="n">
         <v>14810.786</v>
       </c>
+      <c r="D26" t="n">
+        <v>0.0077</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -749,6 +788,9 @@
       <c r="C27" t="n">
         <v>16755.395</v>
       </c>
+      <c r="D27" t="n">
+        <v>0.0092</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -760,6 +802,9 @@
       <c r="C28" t="n">
         <v>28257.898</v>
       </c>
+      <c r="D28" t="n">
+        <v>0.0134</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -771,6 +816,9 @@
       <c r="C29" t="n">
         <v>33833.413</v>
       </c>
+      <c r="D29" t="n">
+        <v>0.017</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -782,22 +830,1274 @@
       <c r="C30" t="n">
         <v>25983.664</v>
       </c>
+      <c r="D30" t="n">
+        <v>0.0108</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PPR/NPP converts wet-weight PP to carbon at 9:1; NPP is the fixed 2019 ensemble median.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>PPR/NPP is blank because no NPP estimate exists for this ecosystem.</t>
+          <t>PPR/NPP converts wet-weight PP to carbon at 9:1 and uses the matching year's NPP ensemble median.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>PPR/NPP is blank for years without NPP; see NPP for availability and provenance.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
+    <col width="75" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="36" customWidth="1" min="14" max="14"/>
+    <col width="65" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Annual net primary production, tonnes carbon per year</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>PPR/NPP uses the ensemble median for the matching catch year. Blank values are unavailable; no year is substituted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>npp_antoinemorel_tC_yr</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>npp_vgpm_tC_yr</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>npp_eppley_tC_yr</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>npp_cbpm_tC_yr</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>npp_cafe_tC_yr</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>ens_median_tC_yr</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>ens_min_tC_yr</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>ens_max_tC_yr</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="K3" s="7" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+      <c r="L3" s="7" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+      <c r="M3" s="7" t="inlineStr">
+        <is>
+          <t>n_models</t>
+        </is>
+      </c>
+      <c r="N3" s="7" t="inlineStr">
+        <is>
+          <t>available_models</t>
+        </is>
+      </c>
+      <c r="O3" s="7" t="inlineStr">
+        <is>
+          <t>ensemble_basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B4" t="n">
+        <v>24369770.79181</v>
+      </c>
+      <c r="G4" t="n">
+        <v>24369770.79181</v>
+      </c>
+      <c r="H4" t="n">
+        <v>24369770.79181</v>
+      </c>
+      <c r="I4" t="n">
+        <v>24369770.79181</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>vgpm: unsupported_year; eppley: unsupported_year; cbpm: unsupported_year; cafe: unsupported_year</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/1998/65dfd93f461846d2/provenance.json</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>antoinemorel</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B5" t="n">
+        <v>24414343.39577016</v>
+      </c>
+      <c r="G5" t="n">
+        <v>24414343.39577016</v>
+      </c>
+      <c r="H5" t="n">
+        <v>24414343.39577016</v>
+      </c>
+      <c r="I5" t="n">
+        <v>24414343.39577016</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>vgpm: unsupported_year; eppley: unsupported_year; cbpm: unsupported_year; cafe: unsupported_year</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/1999/4b1cb2d6cba203fb/provenance.json</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>antoinemorel</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B6" t="n">
+        <v>29071646.37542915</v>
+      </c>
+      <c r="G6" t="n">
+        <v>29071646.37542915</v>
+      </c>
+      <c r="H6" t="n">
+        <v>29071646.37542915</v>
+      </c>
+      <c r="I6" t="n">
+        <v>29071646.37542915</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>vgpm: unsupported_year; eppley: unsupported_year; cbpm: unsupported_year; cafe: unsupported_year</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2000/4bea86f4cd09bd55/provenance.json</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>antoinemorel</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B7" t="n">
+        <v>25544712.27448079</v>
+      </c>
+      <c r="G7" t="n">
+        <v>25544712.27448079</v>
+      </c>
+      <c r="H7" t="n">
+        <v>25544712.27448079</v>
+      </c>
+      <c r="I7" t="n">
+        <v>25544712.27448079</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>vgpm: unsupported_year; eppley: unsupported_year; cbpm: unsupported_year; cafe: unsupported_year</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2001/0ec8617947fb90b9/provenance.json</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>antoinemorel</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B8" t="n">
+        <v>22634910.27539738</v>
+      </c>
+      <c r="G8" t="n">
+        <v>22634910.27539738</v>
+      </c>
+      <c r="H8" t="n">
+        <v>22634910.27539738</v>
+      </c>
+      <c r="I8" t="n">
+        <v>22634910.27539738</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>vgpm: unsupported_year; eppley: unsupported_year; cbpm: unsupported_year; cafe: unsupported_year</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2002/3789d747c9365882/provenance.json</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>antoinemorel</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B9" t="n">
+        <v>25794823.22621515</v>
+      </c>
+      <c r="C9" t="n">
+        <v>15500785.01113383</v>
+      </c>
+      <c r="D9" t="n">
+        <v>14246371.38473469</v>
+      </c>
+      <c r="E9" t="n">
+        <v>34716093.8217854</v>
+      </c>
+      <c r="F9" t="n">
+        <v>47149107.35833752</v>
+      </c>
+      <c r="G9" t="n">
+        <v>25794823.22621515</v>
+      </c>
+      <c r="H9" t="n">
+        <v>14246371.38473469</v>
+      </c>
+      <c r="I9" t="n">
+        <v>47149107.35833752</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2003/c3a820791e3378ef/provenance.json</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>5</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B10" t="n">
+        <v>23489983.80252743</v>
+      </c>
+      <c r="C10" t="n">
+        <v>13994393.33222051</v>
+      </c>
+      <c r="D10" t="n">
+        <v>12867794.75104248</v>
+      </c>
+      <c r="E10" t="n">
+        <v>32303371.40914534</v>
+      </c>
+      <c r="F10" t="n">
+        <v>42796877.96217759</v>
+      </c>
+      <c r="G10" t="n">
+        <v>23489983.80252743</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12867794.75104248</v>
+      </c>
+      <c r="I10" t="n">
+        <v>42796877.96217759</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2004/f4cd3b4c7fc3dd8b/provenance.json</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>5</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B11" t="n">
+        <v>27848433.5947679</v>
+      </c>
+      <c r="C11" t="n">
+        <v>17081862.26781292</v>
+      </c>
+      <c r="D11" t="n">
+        <v>15449090.59791602</v>
+      </c>
+      <c r="E11" t="n">
+        <v>35559185.45937164</v>
+      </c>
+      <c r="F11" t="n">
+        <v>47321141.24398717</v>
+      </c>
+      <c r="G11" t="n">
+        <v>27848433.5947679</v>
+      </c>
+      <c r="H11" t="n">
+        <v>15449090.59791602</v>
+      </c>
+      <c r="I11" t="n">
+        <v>47321141.24398717</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2005/4bdcca026379c2bd/provenance.json</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>5</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B12" t="n">
+        <v>23660368.54533892</v>
+      </c>
+      <c r="C12" t="n">
+        <v>14365722.30867757</v>
+      </c>
+      <c r="D12" t="n">
+        <v>12750984.52792636</v>
+      </c>
+      <c r="E12" t="n">
+        <v>29459489.77650084</v>
+      </c>
+      <c r="F12" t="n">
+        <v>40871543.01796247</v>
+      </c>
+      <c r="G12" t="n">
+        <v>23660368.54533892</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12750984.52792636</v>
+      </c>
+      <c r="I12" t="n">
+        <v>40871543.01796247</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2006/3ea13e28f3d7c994/provenance.json</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>5</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B13" t="n">
+        <v>24901484.78438266</v>
+      </c>
+      <c r="C13" t="n">
+        <v>14560905.22444684</v>
+      </c>
+      <c r="D13" t="n">
+        <v>13394485.15101053</v>
+      </c>
+      <c r="E13" t="n">
+        <v>32470891.19108248</v>
+      </c>
+      <c r="F13" t="n">
+        <v>40395377.58112597</v>
+      </c>
+      <c r="G13" t="n">
+        <v>24901484.78438266</v>
+      </c>
+      <c r="H13" t="n">
+        <v>13394485.15101053</v>
+      </c>
+      <c r="I13" t="n">
+        <v>40395377.58112597</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2007/af2057f32254ca19/provenance.json</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>5</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B14" t="n">
+        <v>21922812.65087019</v>
+      </c>
+      <c r="C14" t="n">
+        <v>13231353.72076329</v>
+      </c>
+      <c r="D14" t="n">
+        <v>11937934.43102127</v>
+      </c>
+      <c r="E14" t="n">
+        <v>27173933.41178992</v>
+      </c>
+      <c r="F14" t="n">
+        <v>39909712.73253152</v>
+      </c>
+      <c r="G14" t="n">
+        <v>21922812.65087019</v>
+      </c>
+      <c r="H14" t="n">
+        <v>11937934.43102127</v>
+      </c>
+      <c r="I14" t="n">
+        <v>39909712.73253152</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2008/51e4a448b1f4148f/provenance.json</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B15" t="n">
+        <v>25685471.69279423</v>
+      </c>
+      <c r="C15" t="n">
+        <v>16155289.91748132</v>
+      </c>
+      <c r="D15" t="n">
+        <v>14622499.82256988</v>
+      </c>
+      <c r="E15" t="n">
+        <v>30944326.79982119</v>
+      </c>
+      <c r="F15" t="n">
+        <v>43089703.67298722</v>
+      </c>
+      <c r="G15" t="n">
+        <v>25685471.69279423</v>
+      </c>
+      <c r="H15" t="n">
+        <v>14622499.82256988</v>
+      </c>
+      <c r="I15" t="n">
+        <v>43089703.67298722</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2009/d16425bc4ac9cb7d/provenance.json</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>5</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B16" t="n">
+        <v>28164428.94238678</v>
+      </c>
+      <c r="C16" t="n">
+        <v>19368288.21828334</v>
+      </c>
+      <c r="D16" t="n">
+        <v>16302081.2456215</v>
+      </c>
+      <c r="E16" t="n">
+        <v>33912899.11393338</v>
+      </c>
+      <c r="F16" t="n">
+        <v>47648233.93884121</v>
+      </c>
+      <c r="G16" t="n">
+        <v>28164428.94238678</v>
+      </c>
+      <c r="H16" t="n">
+        <v>16302081.2456215</v>
+      </c>
+      <c r="I16" t="n">
+        <v>47648233.93884121</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2010/5d2cc2c9685a81c9/provenance.json</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>5</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B17" t="n">
+        <v>25687123.87725379</v>
+      </c>
+      <c r="C17" t="n">
+        <v>17240177.85876979</v>
+      </c>
+      <c r="D17" t="n">
+        <v>15013888.06770988</v>
+      </c>
+      <c r="E17" t="n">
+        <v>28811046.15208645</v>
+      </c>
+      <c r="F17" t="n">
+        <v>47865600.88380044</v>
+      </c>
+      <c r="G17" t="n">
+        <v>25687123.87725379</v>
+      </c>
+      <c r="H17" t="n">
+        <v>15013888.06770988</v>
+      </c>
+      <c r="I17" t="n">
+        <v>47865600.88380044</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2011/a6c24b780ceeb354/provenance.json</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>5</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B18" t="n">
+        <v>25057226.51283893</v>
+      </c>
+      <c r="C18" t="n">
+        <v>16008999.27372082</v>
+      </c>
+      <c r="D18" t="n">
+        <v>14470518.45214215</v>
+      </c>
+      <c r="E18" t="n">
+        <v>33222710.44303272</v>
+      </c>
+      <c r="F18" t="n">
+        <v>45610425.10623424</v>
+      </c>
+      <c r="G18" t="n">
+        <v>25057226.51283893</v>
+      </c>
+      <c r="H18" t="n">
+        <v>14470518.45214215</v>
+      </c>
+      <c r="I18" t="n">
+        <v>45610425.10623424</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2012/2fd3c52e363d2259/provenance.json</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>5</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B19" t="n">
+        <v>26554918.73236408</v>
+      </c>
+      <c r="C19" t="n">
+        <v>18624851.11065771</v>
+      </c>
+      <c r="D19" t="n">
+        <v>16102795.96994848</v>
+      </c>
+      <c r="E19" t="n">
+        <v>25693295.08273279</v>
+      </c>
+      <c r="F19" t="n">
+        <v>47304265.91678242</v>
+      </c>
+      <c r="G19" t="n">
+        <v>25693295.08273279</v>
+      </c>
+      <c r="H19" t="n">
+        <v>16102795.96994848</v>
+      </c>
+      <c r="I19" t="n">
+        <v>47304265.91678242</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2013/821becabd572bab5/provenance.json</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>5</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B20" t="n">
+        <v>28569047.75000314</v>
+      </c>
+      <c r="C20" t="n">
+        <v>19628715.72749856</v>
+      </c>
+      <c r="D20" t="n">
+        <v>17785835.14809608</v>
+      </c>
+      <c r="E20" t="n">
+        <v>24751915.4884317</v>
+      </c>
+      <c r="F20" t="n">
+        <v>50549700.60970985</v>
+      </c>
+      <c r="G20" t="n">
+        <v>24751915.4884317</v>
+      </c>
+      <c r="H20" t="n">
+        <v>17785835.14809608</v>
+      </c>
+      <c r="I20" t="n">
+        <v>50549700.60970985</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2014/c9d1725dde41256d/provenance.json</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>5</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B21" t="n">
+        <v>26462788.21470868</v>
+      </c>
+      <c r="C21" t="n">
+        <v>17062845.68731913</v>
+      </c>
+      <c r="D21" t="n">
+        <v>15533642.2635871</v>
+      </c>
+      <c r="E21" t="n">
+        <v>21503657.36823525</v>
+      </c>
+      <c r="F21" t="n">
+        <v>43103647.59272163</v>
+      </c>
+      <c r="G21" t="n">
+        <v>21503657.36823525</v>
+      </c>
+      <c r="H21" t="n">
+        <v>15533642.2635871</v>
+      </c>
+      <c r="I21" t="n">
+        <v>43103647.59272163</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2015/9d39afaaa8b014f8/provenance.json</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>5</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B22" t="n">
+        <v>28852652.57470907</v>
+      </c>
+      <c r="C22" t="n">
+        <v>20185368.78742022</v>
+      </c>
+      <c r="D22" t="n">
+        <v>19351794.01601617</v>
+      </c>
+      <c r="E22" t="n">
+        <v>17892815.661385</v>
+      </c>
+      <c r="F22" t="n">
+        <v>49074702.60150029</v>
+      </c>
+      <c r="G22" t="n">
+        <v>20185368.78742022</v>
+      </c>
+      <c r="H22" t="n">
+        <v>17892815.661385</v>
+      </c>
+      <c r="I22" t="n">
+        <v>49074702.60150029</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2016/cfbe2d742214e408/provenance.json</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>5</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B23" t="n">
+        <v>24831717.77100199</v>
+      </c>
+      <c r="C23" t="n">
+        <v>18404506.87600129</v>
+      </c>
+      <c r="D23" t="n">
+        <v>15832532.44430518</v>
+      </c>
+      <c r="E23" t="n">
+        <v>23465092.16858066</v>
+      </c>
+      <c r="F23" t="n">
+        <v>43218302.16373868</v>
+      </c>
+      <c r="G23" t="n">
+        <v>23465092.16858066</v>
+      </c>
+      <c r="H23" t="n">
+        <v>15832532.44430518</v>
+      </c>
+      <c r="I23" t="n">
+        <v>43218302.16373868</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2017/e85bc3c6652e1ebf/provenance.json</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>5</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B24" t="n">
+        <v>22069955.63153723</v>
+      </c>
+      <c r="C24" t="n">
+        <v>16451858.97447017</v>
+      </c>
+      <c r="D24" t="n">
+        <v>14285730.01282462</v>
+      </c>
+      <c r="E24" t="n">
+        <v>27708024.02330457</v>
+      </c>
+      <c r="F24" t="n">
+        <v>42942462.9772351</v>
+      </c>
+      <c r="G24" t="n">
+        <v>22069955.63153723</v>
+      </c>
+      <c r="H24" t="n">
+        <v>14285730.01282462</v>
+      </c>
+      <c r="I24" t="n">
+        <v>42942462.9772351</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2018/786b5184701484b9/provenance.json</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>5</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B25" t="n">
+        <v>26749355.09719533</v>
+      </c>
+      <c r="C25" t="n">
+        <v>19367532.31820663</v>
+      </c>
+      <c r="D25" t="n">
+        <v>17163881.40960025</v>
+      </c>
+      <c r="E25" t="n">
+        <v>38519359.25488868</v>
+      </c>
+      <c r="F25" t="n">
+        <v>49495000.83767059</v>
+      </c>
+      <c r="G25" t="n">
+        <v>26749355.09719533</v>
+      </c>
+      <c r="H25" t="n">
+        <v>17163881.40960025</v>
+      </c>
+      <c r="I25" t="n">
+        <v>49495000.83767059</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2019/e82a6f61f15e47c4/provenance.json</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>5</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:O25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1964,188 +3264,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Specific PPR for EEZ_074</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Simple method, applied per taxon: SPPR = (1/TE)^(TL-1), TE = 0.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>taxon</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>trophic_level</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>sppr_simple</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Rajiformes</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="C5" t="n">
-        <v>407.380278</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Macrourus</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="C6" t="n">
-        <v>380.189396</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Antimora rostrata</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="C7" t="n">
-        <v>380.189396</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Nototheniidae</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="C8" t="n">
-        <v>269.15348</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Muraenolepis</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="C9" t="n">
-        <v>251.188643</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Channichthyidae</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="C10" t="n">
-        <v>218.776162</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Marine fishes not identified</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="C11" t="n">
-        <v>190.546072</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Lepidonotothen squamifrons</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="C12" t="n">
-        <v>123.026877</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Lithodidae</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="C13" t="n">
-        <v>66.069345</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Cnidaria</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="C14" t="n">
-        <v>31.622777</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>No Ecopath model has been extracted for this ecosystem yet,</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>so the network-based SPPR methods are not available here.</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>No final mappings are available for this ecosystem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Models without a recorded mapping are not assigned invented taxon groups or weights.</t>
         </is>
       </c>
     </row>
@@ -2160,43 +3295,188 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>Group SPPR: all</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>All basal sources, including imports. Models are separate. Blank means unavailable, not zero.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>group_name</t>
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Specific PPR for EEZ_074</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Simple method, applied per taxon: SPPR = (1/TE)^(TL-1), TE = 0.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>taxon</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>trophic_level</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>sppr_simple</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>No extracted model is available for this ecosystem.</t>
+          <t>Rajiformes</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="C5" t="n">
+        <v>407.380278</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Macrourus</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="C6" t="n">
+        <v>380.189396</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Antimora rostrata</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="C7" t="n">
+        <v>380.189396</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Nototheniidae</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="C8" t="n">
+        <v>269.15348</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Muraenolepis</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="C9" t="n">
+        <v>251.188643</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Channichthyidae</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="C10" t="n">
+        <v>218.776162</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Marine fishes not identified</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="C11" t="n">
+        <v>190.546072</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Lepidonotothen squamifrons</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="C12" t="n">
+        <v>123.026877</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Lithodidae</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="C13" t="n">
+        <v>66.069345</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Cnidaria</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C14" t="n">
+        <v>31.622777</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>No Ecopath model has been extracted for this ecosystem yet,</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>so the network-based SPPR methods are not available here.</t>
         </is>
       </c>
     </row>
@@ -2221,14 +3501,14 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Group SPPR: inner</t>
+          <t>Group SPPR: all</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Internal sources: primary producers and detritus; excludes imports. Models are separate. Blank means unavailable, not zero.</t>
+          <t>All basal sources, including imports. Models are separate. Blank means unavailable, not zero.</t>
         </is>
       </c>
     </row>
@@ -2272,14 +3552,14 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Group SPPR: PP</t>
+          <t>Group SPPR: inner</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Primary producers only; excludes detritus and imports. Models are separate. Blank means unavailable, not zero.</t>
+          <t>Internal sources: primary producers and detritus; excludes imports. Models are separate. Blank means unavailable, not zero.</t>
         </is>
       </c>
     </row>
@@ -2308,6 +3588,57 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Group SPPR: PP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Primary producers only; excludes detritus and imports. Models are separate. Blank means unavailable, not zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>group_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>No extracted model is available for this ecosystem.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2393,7 +3724,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3096,32 +4427,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>No net primary production estimate is available for this ecosystem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>NPP currently covers LME and High Seas units only, not EEZs.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>